--- a/output/pdf_financials_xlsx/SKUR.xlsx
+++ b/output/pdf_financials_xlsx/SKUR.xlsx
@@ -1920,13 +1920,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>6.069868</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>6.327479</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>6.904442</v>
       </c>
     </row>
     <row r="93">
@@ -3197,7 +3197,11 @@
           <t>Reserves (Notes 5 and 7)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -3501,7 +3505,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
         <v>6.069868</v>
       </c>

--- a/output/pdf_financials_xlsx/SKUR.xlsx
+++ b/output/pdf_financials_xlsx/SKUR.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.100866</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.015537</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.009952000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-4.754103</v>
+        <v>-4.854969</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.967131</v>
+        <v>-1.982668</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.491608</v>
+        <v>-3.50156</v>
       </c>
     </row>
     <row r="28">
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-4.52607</v>
+        <v>-4.626936</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.737723</v>
+        <v>-1.75326</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.268392</v>
+        <v>-3.278344</v>
       </c>
     </row>
     <row r="30">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-833.2511018406354</v>
+        <v>-851.8205684282616</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-363.7671602798397</v>
+        <v>-367.0196063654747</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-799.6907319913777</v>
+        <v>-802.1257282111636</v>
       </c>
     </row>
     <row r="31">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">

--- a/output/pdf_financials_xlsx/SKUR.xlsx
+++ b/output/pdf_financials_xlsx/SKUR.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.671883</v>
+        <v>1.01964</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.229712</v>
+        <v>0.289712</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.522128</v>
+        <v>0.920995</v>
       </c>
     </row>
     <row r="8">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2.792071</v>
+        <v>3.139828</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>2.482631</v>
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-2.248889</v>
+        <v>-2.596646</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-2.004929</v>
@@ -4971,7 +4971,11 @@
           <t>Director’s fees (Notes 7 and 8)</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -6207,7 +6211,11 @@
           <t>Director’s fees (Notes 5 and 6)</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E116" s="5" t="n">
         <v>0.347757</v>
       </c>
